--- a/tests/datastructure/variable_definition.xlsx
+++ b/tests/datastructure/variable_definition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="128">
   <si>
     <t xml:space="preserve">VaribleID</t>
   </si>
@@ -52,6 +52,18 @@
     <t xml:space="preserve">VariableLowerBound</t>
   </si>
   <si>
+    <t xml:space="preserve">Potentiaalberekening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limitstate_Uplift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limitstate_Heave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limitstate_Piping</t>
+  </si>
+  <si>
     <t xml:space="preserve">dist_L_geom</t>
   </si>
   <si>
@@ -64,6 +76,9 @@
     <t xml:space="preserve">Input</t>
   </si>
   <si>
+    <t xml:space="preserve">input</t>
+  </si>
+  <si>
     <t xml:space="preserve">dist_BUT</t>
   </si>
   <si>
@@ -175,6 +190,9 @@
     <t xml:space="preserve">Weerstand van de deklaag in het achterland</t>
   </si>
   <si>
+    <t xml:space="preserve">Input, can also be calculated</t>
+  </si>
+  <si>
     <t xml:space="preserve">m_u</t>
   </si>
   <si>
@@ -226,6 +244,9 @@
     <t xml:space="preserve">Dempingsfactor bij uittredepunt</t>
   </si>
   <si>
+    <t xml:space="preserve">output</t>
+  </si>
+  <si>
     <t xml:space="preserve">pot_exit</t>
   </si>
   <si>
@@ -365,6 +386,24 @@
   </si>
   <si>
     <t xml:space="preserve">Geohydrologische weerstand van het achterland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F_u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veiligheidsfactor Uplift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veiligheidsfactor Heave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veiligheidsfactor Piping</t>
   </si>
 </sst>
 </file>
@@ -466,19 +505,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,19 +713,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="68.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="22.02"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.85"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -720,675 +763,736 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="E23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="E33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="4" t="s">
+    </row>
+    <row r="34" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C40" s="1" t="s">
+      <c r="E36" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="D37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="D40" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="D41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>32</v>
+      <c r="C44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/tests/datastructure/variable_definition.xlsx
+++ b/tests/datastructure/variable_definition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="136">
   <si>
     <t xml:space="preserve">VaribleID</t>
   </si>
@@ -46,12 +46,12 @@
     <t xml:space="preserve">VariableDefaulValue</t>
   </si>
   <si>
+    <t xml:space="preserve">VariableLowerBound</t>
+  </si>
+  <si>
     <t xml:space="preserve">VariableUpperBound</t>
   </si>
   <si>
-    <t xml:space="preserve">VariableLowerBound</t>
-  </si>
-  <si>
     <t xml:space="preserve">Potentiaalberekening</t>
   </si>
   <si>
@@ -76,6 +76,9 @@
     <t xml:space="preserve">Input</t>
   </si>
   <si>
+    <t xml:space="preserve">none, deterministic</t>
+  </si>
+  <si>
     <t xml:space="preserve">input</t>
   </si>
   <si>
@@ -118,6 +121,12 @@
     <t xml:space="preserve">Geschematiseerde top van het zak in het vak</t>
   </si>
   <si>
+    <t xml:space="preserve">normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_stdev</t>
+  </si>
+  <si>
     <t xml:space="preserve">gamma_sat_deklaag</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t xml:space="preserve">kN/m^3</t>
   </si>
   <si>
+    <t xml:space="preserve">lognormal, shift 10</t>
+  </si>
+  <si>
     <t xml:space="preserve">D_deklaag</t>
   </si>
   <si>
@@ -136,6 +148,9 @@
     <t xml:space="preserve">Calculated</t>
   </si>
   <si>
+    <t xml:space="preserve">normal, by functional design &gt;0,1 m</t>
+  </si>
+  <si>
     <t xml:space="preserve">gamma_w</t>
   </si>
   <si>
@@ -154,6 +169,12 @@
     <t xml:space="preserve">m^2/dag</t>
   </si>
   <si>
+    <t xml:space="preserve">lognormal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_vc</t>
+  </si>
+  <si>
     <t xml:space="preserve">D_wvp</t>
   </si>
   <si>
@@ -230,6 +251,9 @@
   </si>
   <si>
     <t xml:space="preserve">Buitenwaterstand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extreme value of CDF</t>
   </si>
   <si>
     <t xml:space="preserve">eta</t>
@@ -410,8 +434,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00E+00"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -500,7 +526,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,6 +545,18 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -713,7 +751,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.76"/>
@@ -726,10 +764,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="22.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.85"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -789,16 +827,26 @@
       <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>2000</v>
+      </c>
       <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O2" s="6"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
@@ -806,16 +854,24 @@
       <c r="E3" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5"/>
       <c r="K3" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
@@ -823,16 +879,24 @@
       <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5"/>
       <c r="K4" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>16</v>
@@ -840,120 +904,202 @@
       <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>5000</v>
+      </c>
       <c r="K5" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>4000</v>
+      </c>
       <c r="K12" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>16</v>
@@ -961,27 +1107,47 @@
       <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>16</v>
@@ -989,511 +1155,710 @@
       <c r="E15" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>56</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="O18" s="6"/>
     </row>
     <row r="19" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="O19" s="6"/>
     </row>
     <row r="20" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="F23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
       <c r="K23" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" s="3" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
       <c r="K25" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
       <c r="K26" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O26" s="6"/>
     </row>
     <row r="27" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="O27" s="6"/>
     </row>
     <row r="28" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="O28" s="6"/>
     </row>
     <row r="29" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="O29" s="6"/>
     </row>
     <row r="30" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0.000208</v>
+      </c>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="O30" s="6"/>
     </row>
     <row r="31" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="O31" s="6"/>
     </row>
     <row r="32" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>1.33E-006</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="O32" s="6"/>
     </row>
     <row r="33" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="O33" s="6"/>
     </row>
     <row r="34" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="O34" s="6"/>
     </row>
     <row r="35" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="O36" s="6"/>
     </row>
     <row r="37" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="3" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="O37" s="6"/>
     </row>
     <row r="38" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="O39" s="6"/>
     </row>
     <row r="40" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="O40" s="6"/>
     </row>
     <row r="41" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="O41" s="6"/>
     </row>
     <row r="42" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="O42" s="6"/>
     </row>
     <row r="43" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="O43" s="6"/>
     </row>
     <row r="44" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="O44" s="6"/>
     </row>
     <row r="45" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="O45" s="6"/>
     </row>
     <row r="46" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="O46" s="6"/>
     </row>
     <row r="47" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="O47" s="6"/>
     </row>
     <row r="48" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="O48" s="6"/>
     </row>
     <row r="49" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="O49" s="6"/>
     </row>
     <row r="50" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="O50" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/tests/datastructure/variable_definition.xlsx
+++ b/tests/datastructure/variable_definition.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsrlnl-my.sharepoint.com/personal/s_kapinga_wsrl_nl/Documents/Documenten/Github/GeoProb-Pipe/tests/datastructure/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_8663580C170AFFC80153070DC51E11F7671CB157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97B5A532-0F96-4EC3-B300-9BB2DEB17627}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Variables" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Variables" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,447 +25,430 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="136">
-  <si>
-    <t xml:space="preserve">VaribleID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableDescription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableUnit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableDistribution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spreidingstype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableDefaulValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableLowerBound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VariableUpperBound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potentiaalberekening</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limitstate_Uplift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limitstate_Heave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limitstate_Piping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_L_geom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afstand van uittredepunt tot geometrische intredelijn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">none, deterministic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">input</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_BUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afstand van uittredepunt tot buitenteenlijn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_BIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afstand van uittredepunt tot binnenteenlijn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3_geom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Afstand van uittredepunt tot Achterlandlengte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bodemhoogte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodemhoogte ter plaatse van uittredepunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m+NAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">polderpeil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Polderpeil ter plaatse van uittredepunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">top_zand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geschematiseerde top van het zak in het vak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_stdev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma_sat_deklaag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gemiddeld volumegewicht van de deklaag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kN/m^3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lognormal, shift 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D_deklaag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dikte van de cohesieve deklaag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal, by functional design &gt;0,1 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma_w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumegewicht van water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kD_wvp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmissiviteit van het watervoerende pakket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m^2/dag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_vc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D_wvp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dikte van het watervoerende pakket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k_wvp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doorlatendheid van het watervoerende pakket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m/d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d_70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70% percentiel van de korrelverdeling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weerstand van de deklaag in het voorland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weerstand van de deklaag in het achterland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input, can also be calculated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m_u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modelfactor voor uplift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modelfactor voor heave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">modelfactor voor piping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i_c_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kritieke heave gradiënt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r_c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reductie van het verval over de deklaag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buitenwaterstand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extreme value of CDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White's weerstandscoefficient (sleepkrachtfactor, constante van White) – Sellmeijer [-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r_exit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dempingsfactor bij uittredepunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pot_exit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theoretische stijghoogte bij uittredepunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h_exit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benedestroomse randvoorwaarde verval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L_kwelweg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwelweglengte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">theta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolweerstandshoek – Sellmeijer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[graden]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d_70_m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referentiewaarde voor de 70% percentiel van de korrelverdeling – Sellmeijer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zwaartekrachtversnelling – 9,81 m/s²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m/s^2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kinematische viscositeit – Sellmeijer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m²/s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gamma_sp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volumieke dichtheid zand onder water – Sellmeijer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d_pot_c_u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grenspotentiaal ten opzicht van maaiveld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dhred</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gereduceerd verval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i_optredend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optredende heave gradient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dhc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kritiek verval Sellmeijer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenstoestand Uplift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenstoestand Heave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grenstoestand Piping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_combin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gecombineerde grenstoestand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geometrische voorlandlengte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dijkzate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lambda_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spreidingslengte van het voorland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lambda_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spreidingslengte van het achterland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geohydrologische weerstand van het voorland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geohydrologische weerstand van het achterland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_u</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veiligheidsfactor Uplift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veiligheidsfactor Heave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veiligheidsfactor Piping</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="137">
+  <si>
+    <t>VaribleID</t>
+  </si>
+  <si>
+    <t>VariableName</t>
+  </si>
+  <si>
+    <t>VariableDescription</t>
+  </si>
+  <si>
+    <t>VariableUnit</t>
+  </si>
+  <si>
+    <t>VariableType</t>
+  </si>
+  <si>
+    <t>VariableDistribution</t>
+  </si>
+  <si>
+    <t>Spreidingstype</t>
+  </si>
+  <si>
+    <t>VariableDefaulValue</t>
+  </si>
+  <si>
+    <t>VariableLowerBound</t>
+  </si>
+  <si>
+    <t>VariableUpperBound</t>
+  </si>
+  <si>
+    <t>Potentiaalberekening</t>
+  </si>
+  <si>
+    <t>limitstate_Uplift</t>
+  </si>
+  <si>
+    <t>limitstate_Heave</t>
+  </si>
+  <si>
+    <t>limitstate_Piping</t>
+  </si>
+  <si>
+    <t>dist_L_geom</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunt tot geometrische intredelijn</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>none, deterministic</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>dist_BUT</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunt tot buitenteenlijn</t>
+  </si>
+  <si>
+    <t>dist_BIT</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunt tot binnenteenlijn</t>
+  </si>
+  <si>
+    <t>L3_geom</t>
+  </si>
+  <si>
+    <t>Afstand van uittredepunt tot Achterlandlengte</t>
+  </si>
+  <si>
+    <t>bodemhoogte</t>
+  </si>
+  <si>
+    <t>Bodemhoogte ter plaatse van uittredepunt</t>
+  </si>
+  <si>
+    <t>m+NAP</t>
+  </si>
+  <si>
+    <t>polderpeil</t>
+  </si>
+  <si>
+    <t>Polderpeil ter plaatse van uittredepunt</t>
+  </si>
+  <si>
+    <t>top_zand</t>
+  </si>
+  <si>
+    <t>Geschematiseerde top van het zak in het vak</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>_stdev</t>
+  </si>
+  <si>
+    <t>gamma_sat_deklaag</t>
+  </si>
+  <si>
+    <t>Gemiddeld volumegewicht van de deklaag</t>
+  </si>
+  <si>
+    <t>kN/m^3</t>
+  </si>
+  <si>
+    <t>lognormal, shift 10</t>
+  </si>
+  <si>
+    <t>D_deklaag</t>
+  </si>
+  <si>
+    <t>Dikte van de cohesieve deklaag</t>
+  </si>
+  <si>
+    <t>Calculated</t>
+  </si>
+  <si>
+    <t>normal, by functional design &gt;0,1 m</t>
+  </si>
+  <si>
+    <t>gamma_w</t>
+  </si>
+  <si>
+    <t>Volumegewicht van water</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t>kD_wvp</t>
+  </si>
+  <si>
+    <t>Transmissiviteit van het watervoerende pakket</t>
+  </si>
+  <si>
+    <t>m^2/dag</t>
+  </si>
+  <si>
+    <t>lognormal</t>
+  </si>
+  <si>
+    <t>_vc</t>
+  </si>
+  <si>
+    <t>D_wvp</t>
+  </si>
+  <si>
+    <t>Dikte van het watervoerende pakket</t>
+  </si>
+  <si>
+    <t>k_wvp</t>
+  </si>
+  <si>
+    <t>Doorlatendheid van het watervoerende pakket</t>
+  </si>
+  <si>
+    <t>m/d</t>
+  </si>
+  <si>
+    <t>d_70</t>
+  </si>
+  <si>
+    <t>70% percentiel van de korrelverdeling</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>Weerstand van de deklaag in het voorland</t>
+  </si>
+  <si>
+    <t>dag</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>Weerstand van de deklaag in het achterland</t>
+  </si>
+  <si>
+    <t>Input, can also be calculated</t>
+  </si>
+  <si>
+    <t>m_u</t>
+  </si>
+  <si>
+    <t>modelfactor voor uplift</t>
+  </si>
+  <si>
+    <t>[-]</t>
+  </si>
+  <si>
+    <t>m_h</t>
+  </si>
+  <si>
+    <t>modelfactor voor heave</t>
+  </si>
+  <si>
+    <t>m_p</t>
+  </si>
+  <si>
+    <t>modelfactor voor piping</t>
+  </si>
+  <si>
+    <t>i_c_h</t>
+  </si>
+  <si>
+    <t>Kritieke heave gradiënt</t>
+  </si>
+  <si>
+    <t>r_c</t>
+  </si>
+  <si>
+    <t>Reductie van het verval over de deklaag</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>Buitenwaterstand</t>
+  </si>
+  <si>
+    <t>extreme value of CDF</t>
+  </si>
+  <si>
+    <t>eta</t>
+  </si>
+  <si>
+    <t>White's weerstandscoefficient (sleepkrachtfactor, constante van White) – Sellmeijer [-]</t>
+  </si>
+  <si>
+    <t>r_exit</t>
+  </si>
+  <si>
+    <t>Dempingsfactor bij uittredepunt</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>pot_exit</t>
+  </si>
+  <si>
+    <t>Theoretische stijghoogte bij uittredepunt</t>
+  </si>
+  <si>
+    <t>h_exit</t>
+  </si>
+  <si>
+    <t>Benedestroomse randvoorwaarde verval</t>
+  </si>
+  <si>
+    <t>L_kwelweg</t>
+  </si>
+  <si>
+    <t>Kwelweglengte</t>
+  </si>
+  <si>
+    <t>theta</t>
+  </si>
+  <si>
+    <t>Rolweerstandshoek – Sellmeijer</t>
+  </si>
+  <si>
+    <t>[graden]</t>
+  </si>
+  <si>
+    <t>d_70_m</t>
+  </si>
+  <si>
+    <t>Referentiewaarde voor de 70% percentiel van de korrelverdeling – Sellmeijer</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>Zwaartekrachtversnelling – 9,81 m/s²</t>
+  </si>
+  <si>
+    <t>m/s^2</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>Kinematische viscositeit – Sellmeijer</t>
+  </si>
+  <si>
+    <t>m²/s</t>
+  </si>
+  <si>
+    <t>gamma_sp</t>
+  </si>
+  <si>
+    <t>Volumieke dichtheid zand onder water – Sellmeijer</t>
+  </si>
+  <si>
+    <t>d_pot_c_u</t>
+  </si>
+  <si>
+    <t>grenspotentiaal ten opzicht van maaiveld</t>
+  </si>
+  <si>
+    <t>dhred</t>
+  </si>
+  <si>
+    <t>Gereduceerd verval</t>
+  </si>
+  <si>
+    <t>i_optredend</t>
+  </si>
+  <si>
+    <t>Optredende heave gradient</t>
+  </si>
+  <si>
+    <t>dhc</t>
+  </si>
+  <si>
+    <t>Kritiek verval Sellmeijer</t>
+  </si>
+  <si>
+    <t>Z_u</t>
+  </si>
+  <si>
+    <t>Grenstoestand Uplift</t>
+  </si>
+  <si>
+    <t>Z_h</t>
+  </si>
+  <si>
+    <t>Grenstoestand Heave</t>
+  </si>
+  <si>
+    <t>Z_p</t>
+  </si>
+  <si>
+    <t>Grenstoestand Piping</t>
+  </si>
+  <si>
+    <t>Z_combin</t>
+  </si>
+  <si>
+    <t>Gecombineerde grenstoestand</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Geometrische voorlandlengte</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>Dijkzate</t>
+  </si>
+  <si>
+    <t>lambda_1</t>
+  </si>
+  <si>
+    <t>Spreidingslengte van het voorland</t>
+  </si>
+  <si>
+    <t>lambda_3</t>
+  </si>
+  <si>
+    <t>Spreidingslengte van het achterland</t>
+  </si>
+  <si>
+    <t>W1</t>
+  </si>
+  <si>
+    <t>Geohydrologische weerstand van het voorland</t>
+  </si>
+  <si>
+    <t>W3</t>
+  </si>
+  <si>
+    <t>Geohydrologische weerstand van het achterland</t>
+  </si>
+  <si>
+    <t>F_u</t>
+  </si>
+  <si>
+    <t>Veiligheidsfactor Uplift</t>
+  </si>
+  <si>
+    <t>F_h</t>
+  </si>
+  <si>
+    <t>Veiligheidsfactor Heave</t>
+  </si>
+  <si>
+    <t>F_p</t>
+  </si>
+  <si>
+    <t>Veiligheidsfactor Piping</t>
+  </si>
+  <si>
+    <t>calculated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.00E+00"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
@@ -470,7 +458,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -486,127 +474,103 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -614,12 +578,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -648,7 +612,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -669,7 +633,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -720,7 +684,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -738,39 +702,38 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O50"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="68.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="22.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.85"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="11.53"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="22" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -814,7 +777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
@@ -830,18 +793,27 @@
       <c r="F2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="5">
         <v>5</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="5">
         <v>2000</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="6"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2"/>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -857,16 +829,25 @@
       <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3"/>
+    </row>
+    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
@@ -882,16 +863,22 @@
       <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="6"/>
-    </row>
-    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4"/>
+    </row>
+    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
@@ -907,18 +894,24 @@
       <c r="F5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="5">
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="5">
         <v>5000</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="6"/>
-    </row>
-    <row r="6" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5"/>
+    </row>
+    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
@@ -934,15 +927,18 @@
       <c r="F6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="5">
         <v>-4</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="5">
         <v>15</v>
       </c>
-      <c r="O6" s="6"/>
-    </row>
-    <row r="7" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6"/>
+    </row>
+    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
@@ -963,9 +959,18 @@
       <c r="K7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O7" s="6"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7"/>
+    </row>
+    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>31</v>
       </c>
@@ -984,15 +989,18 @@
       <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="5">
         <v>-18</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="5">
         <v>15</v>
       </c>
-      <c r="O8" s="6"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8"/>
+    </row>
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>35</v>
       </c>
@@ -1011,15 +1019,15 @@
       <c r="G9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="5">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="5">
         <v>22</v>
       </c>
-      <c r="O9" s="6"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O9"/>
+    </row>
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>39</v>
       </c>
@@ -1035,13 +1043,13 @@
       <c r="F10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="5">
         <v>0.1</v>
       </c>
       <c r="J10" s="5"/>
-      <c r="O10" s="6"/>
-    </row>
-    <row r="11" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O10"/>
+    </row>
+    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
@@ -1057,14 +1065,14 @@
       <c r="F11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="3">
         <v>9.81</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
-      <c r="O11" s="6"/>
-    </row>
-    <row r="12" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O11"/>
+    </row>
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
@@ -1083,18 +1091,27 @@
       <c r="G12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="5">
         <v>1.5</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="5">
         <v>4000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="6"/>
-    </row>
-    <row r="13" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12"/>
+    </row>
+    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>51</v>
       </c>
@@ -1113,15 +1130,18 @@
       <c r="G13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I13" s="5">
         <v>1.5</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="5">
         <v>60</v>
       </c>
-      <c r="O13" s="6"/>
-    </row>
-    <row r="14" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13"/>
+    </row>
+    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>53</v>
       </c>
@@ -1134,15 +1154,15 @@
       <c r="E14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="5">
         <v>1</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="5">
         <v>110</v>
       </c>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O14"/>
+    </row>
+    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
@@ -1161,15 +1181,18 @@
       <c r="G15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0.00015</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="O15" s="6"/>
-    </row>
-    <row r="16" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="6">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="J15" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15"/>
+    </row>
+    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
@@ -1193,9 +1216,12 @@
       <c r="K16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O16" s="6"/>
-    </row>
-    <row r="17" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16"/>
+    </row>
+    <row r="17" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
@@ -1219,9 +1245,9 @@
       <c r="K17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O17" s="6"/>
-    </row>
-    <row r="18" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O17"/>
+    </row>
+    <row r="18" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>64</v>
       </c>
@@ -1242,9 +1268,12 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
-      <c r="O18" s="6"/>
-    </row>
-    <row r="19" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O18"/>
+    </row>
+    <row r="19" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>67</v>
       </c>
@@ -1265,9 +1294,12 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
-      <c r="O19" s="6"/>
-    </row>
-    <row r="20" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19"/>
+    </row>
+    <row r="20" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>69</v>
       </c>
@@ -1288,9 +1320,12 @@
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
-      <c r="O20" s="6"/>
-    </row>
-    <row r="21" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O20"/>
+    </row>
+    <row r="21" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>71</v>
       </c>
@@ -1306,14 +1341,17 @@
       <c r="F21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="5">
         <v>0.3</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>73</v>
       </c>
@@ -1329,14 +1367,17 @@
       <c r="F22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="5">
         <v>0.3</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
-      <c r="O22" s="6"/>
-    </row>
-    <row r="23" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>75</v>
       </c>
@@ -1357,9 +1398,18 @@
       <c r="K23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O23" s="6"/>
-    </row>
-    <row r="24" s="3" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="2:15" s="3" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>78</v>
       </c>
@@ -1375,14 +1425,14 @@
       <c r="F24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="3">
         <v>0.25</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-      <c r="O24" s="6"/>
-    </row>
-    <row r="25" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>80</v>
       </c>
@@ -1400,9 +1450,9 @@
       <c r="K25" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O25" s="6"/>
-    </row>
-    <row r="26" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O25"/>
+    </row>
+    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>83</v>
       </c>
@@ -1420,9 +1470,15 @@
       <c r="K26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O26" s="6"/>
-    </row>
-    <row r="27" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O26"/>
+    </row>
+    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>85</v>
       </c>
@@ -1437,9 +1493,12 @@
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
-      <c r="O27" s="6"/>
-    </row>
-    <row r="28" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O27"/>
+    </row>
+    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>87</v>
       </c>
@@ -1454,9 +1513,12 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
-      <c r="O28" s="6"/>
-    </row>
-    <row r="29" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O28"/>
+    </row>
+    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>89</v>
       </c>
@@ -1472,14 +1534,17 @@
       <c r="F29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="5">
         <v>37</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
-      <c r="O29" s="6"/>
-    </row>
-    <row r="30" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O29"/>
+    </row>
+    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>92</v>
       </c>
@@ -1495,14 +1560,17 @@
       <c r="F30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H30" s="7" t="n">
-        <v>0.000208</v>
+      <c r="H30" s="6">
+        <v>2.0799999999999999E-4</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
-      <c r="O30" s="6"/>
-    </row>
-    <row r="31" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30"/>
+    </row>
+    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>94</v>
       </c>
@@ -1518,14 +1586,17 @@
       <c r="F31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="3">
         <v>9.81</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="O31" s="6"/>
-    </row>
-    <row r="32" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O31"/>
+    </row>
+    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>97</v>
       </c>
@@ -1541,14 +1612,17 @@
       <c r="F32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H32" s="7" t="n">
-        <v>1.33E-006</v>
+      <c r="H32" s="6">
+        <v>1.33E-6</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="O32" s="6"/>
-    </row>
-    <row r="33" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O32"/>
+    </row>
+    <row r="33" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>100</v>
       </c>
@@ -1564,14 +1638,17 @@
       <c r="F33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="5">
         <v>26</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="O33" s="6"/>
-    </row>
-    <row r="34" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O33"/>
+    </row>
+    <row r="34" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>102</v>
       </c>
@@ -1586,9 +1663,12 @@
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="O34" s="6"/>
-    </row>
-    <row r="35" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L34" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>104</v>
       </c>
@@ -1603,9 +1683,12 @@
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="O35" s="6"/>
-    </row>
-    <row r="36" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N35" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O35"/>
+    </row>
+    <row r="36" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
@@ -1620,9 +1703,12 @@
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
-      <c r="O36" s="6"/>
-    </row>
-    <row r="37" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
         <v>108</v>
       </c>
@@ -1637,9 +1723,12 @@
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="O37" s="6"/>
-    </row>
-    <row r="38" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O37"/>
+    </row>
+    <row r="38" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
         <v>110</v>
       </c>
@@ -1654,9 +1743,12 @@
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="O38" s="6"/>
-    </row>
-    <row r="39" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O38"/>
+    </row>
+    <row r="39" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
         <v>112</v>
       </c>
@@ -1671,9 +1763,12 @@
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="O39" s="6"/>
-    </row>
-    <row r="40" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O39"/>
+    </row>
+    <row r="40" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3" t="s">
         <v>114</v>
       </c>
@@ -1688,9 +1783,12 @@
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="O40" s="6"/>
-    </row>
-    <row r="41" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N40" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3" t="s">
         <v>116</v>
       </c>
@@ -1705,9 +1803,18 @@
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="O41" s="6"/>
-    </row>
-    <row r="42" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41"/>
+    </row>
+    <row r="42" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>118</v>
       </c>
@@ -1722,9 +1829,12 @@
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="O42" s="6"/>
-    </row>
-    <row r="43" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
         <v>120</v>
       </c>
@@ -1739,9 +1849,12 @@
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="O43" s="6"/>
-    </row>
-    <row r="44" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O43"/>
+    </row>
+    <row r="44" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
         <v>122</v>
       </c>
@@ -1756,9 +1869,12 @@
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
-      <c r="O44" s="6"/>
-    </row>
-    <row r="45" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>124</v>
       </c>
@@ -1773,9 +1889,12 @@
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="O45" s="6"/>
-    </row>
-    <row r="46" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K45" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O45"/>
+    </row>
+    <row r="46" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
         <v>126</v>
       </c>
@@ -1790,9 +1909,12 @@
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
-      <c r="O46" s="6"/>
-    </row>
-    <row r="47" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O46"/>
+    </row>
+    <row r="47" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
         <v>128</v>
       </c>
@@ -1807,9 +1929,12 @@
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="O47" s="6"/>
-    </row>
-    <row r="48" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="O47"/>
+    </row>
+    <row r="48" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
         <v>130</v>
       </c>
@@ -1824,9 +1949,12 @@
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
-      <c r="O48" s="6"/>
-    </row>
-    <row r="49" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L48" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O48"/>
+    </row>
+    <row r="49" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="3" t="s">
         <v>132</v>
       </c>
@@ -1841,9 +1969,12 @@
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
-      <c r="O49" s="6"/>
-    </row>
-    <row r="50" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O49"/>
+    </row>
+    <row r="50" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="3" t="s">
         <v>134</v>
       </c>
@@ -1858,15 +1989,13 @@
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
-      <c r="O50" s="6"/>
+      <c r="N50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O50"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/tests/datastructure/variable_definition.xlsx
+++ b/tests/datastructure/variable_definition.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsrlnl-my.sharepoint.com/personal/s_kapinga_wsrl_nl/Documents/Documenten/Github/GeoProb-Pipe/tests/datastructure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsrlnl-my.sharepoint.com/personal/a_methorst_wsrl_nl/Documents/Bureaublad/GeoProb-Pipe/tests/datastructure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_8663580C170AFFC80153070DC51E11F7671CB157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97B5A532-0F96-4EC3-B300-9BB2DEB17627}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_8663580C170AFFC80153070DC51E11F7671CB157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D4C4065-DAEC-4DDA-BCBD-9CDBD3D0D35B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variables" sheetId="1" r:id="rId1"/>
@@ -69,9 +69,6 @@
     <t>limitstate_Piping</t>
   </si>
   <si>
-    <t>dist_L_geom</t>
-  </si>
-  <si>
     <t>Afstand van uittredepunt tot geometrische intredelijn</t>
   </si>
   <si>
@@ -87,21 +84,12 @@
     <t>input</t>
   </si>
   <si>
-    <t>dist_BUT</t>
-  </si>
-  <si>
     <t>Afstand van uittredepunt tot buitenteenlijn</t>
   </si>
   <si>
-    <t>dist_BIT</t>
-  </si>
-  <si>
     <t>Afstand van uittredepunt tot binnenteenlijn</t>
   </si>
   <si>
-    <t>L3_geom</t>
-  </si>
-  <si>
     <t>Afstand van uittredepunt tot Achterlandlengte</t>
   </si>
   <si>
@@ -144,9 +132,6 @@
     <t>lognormal, shift 10</t>
   </si>
   <si>
-    <t>D_deklaag</t>
-  </si>
-  <si>
     <t>Dikte van de cohesieve deklaag</t>
   </si>
   <si>
@@ -156,9 +141,6 @@
     <t>normal, by functional design &gt;0,1 m</t>
   </si>
   <si>
-    <t>gamma_w</t>
-  </si>
-  <si>
     <t>Volumegewicht van water</t>
   </si>
   <si>
@@ -195,9 +177,6 @@
     <t>m/d</t>
   </si>
   <si>
-    <t>d_70</t>
-  </si>
-  <si>
     <t>70% percentiel van de korrelverdeling</t>
   </si>
   <si>
@@ -246,15 +225,6 @@
     <t>Kritieke heave gradiënt</t>
   </si>
   <si>
-    <t>r_c</t>
-  </si>
-  <si>
-    <t>Reductie van het verval over de deklaag</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
     <t>Buitenwaterstand</t>
   </si>
   <si>
@@ -276,9 +246,6 @@
     <t>output</t>
   </si>
   <si>
-    <t>pot_exit</t>
-  </si>
-  <si>
     <t>Theoretische stijghoogte bij uittredepunt</t>
   </si>
   <si>
@@ -303,9 +270,6 @@
     <t>[graden]</t>
   </si>
   <si>
-    <t>d_70_m</t>
-  </si>
-  <si>
     <t>Referentiewaarde voor de 70% percentiel van de korrelverdeling – Sellmeijer</t>
   </si>
   <si>
@@ -327,33 +291,18 @@
     <t>m²/s</t>
   </si>
   <si>
-    <t>gamma_sp</t>
-  </si>
-  <si>
     <t>Volumieke dichtheid zand onder water – Sellmeijer</t>
   </si>
   <si>
-    <t>d_pot_c_u</t>
-  </si>
-  <si>
     <t>grenspotentiaal ten opzicht van maaiveld</t>
   </si>
   <si>
-    <t>dhred</t>
-  </si>
-  <si>
     <t>Gereduceerd verval</t>
   </si>
   <si>
-    <t>i_optredend</t>
-  </si>
-  <si>
     <t>Optredende heave gradient</t>
   </si>
   <si>
-    <t>dhc</t>
-  </si>
-  <si>
     <t>Kritiek verval Sellmeijer</t>
   </si>
   <si>
@@ -375,9 +324,6 @@
     <t>Grenstoestand Piping</t>
   </si>
   <si>
-    <t>Z_combin</t>
-  </si>
-  <si>
     <t>Gecombineerde grenstoestand</t>
   </si>
   <si>
@@ -393,15 +339,9 @@
     <t>Dijkzate</t>
   </si>
   <si>
-    <t>lambda_1</t>
-  </si>
-  <si>
     <t>Spreidingslengte van het voorland</t>
   </si>
   <si>
-    <t>lambda_3</t>
-  </si>
-  <si>
     <t>Spreidingslengte van het achterland</t>
   </si>
   <si>
@@ -436,6 +376,66 @@
   </si>
   <si>
     <t>calculated</t>
+  </si>
+  <si>
+    <t>L_intrede</t>
+  </si>
+  <si>
+    <t>L_but</t>
+  </si>
+  <si>
+    <t>L_bit</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>d_deklaag</t>
+  </si>
+  <si>
+    <t>gamma_water</t>
+  </si>
+  <si>
+    <t>d70</t>
+  </si>
+  <si>
+    <t>r_c_deklaag</t>
+  </si>
+  <si>
+    <t>Reductieconstante van het verval over de deklaag</t>
+  </si>
+  <si>
+    <t>buitenwaterstand</t>
+  </si>
+  <si>
+    <t>d70_m</t>
+  </si>
+  <si>
+    <t>gamma_korrel</t>
+  </si>
+  <si>
+    <t>phi_exit</t>
+  </si>
+  <si>
+    <t>dh_red</t>
+  </si>
+  <si>
+    <t>i_exit</t>
+  </si>
+  <si>
+    <t>dh_c</t>
+  </si>
+  <si>
+    <t>dphi_c_u</t>
+  </si>
+  <si>
+    <t>Z_combi</t>
+  </si>
+  <si>
+    <t>lambda1</t>
+  </si>
+  <si>
+    <t>lambda3</t>
   </si>
 </sst>
 </file>
@@ -465,12 +465,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -500,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -516,6 +522,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -715,25 +727,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O50"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="68.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="1" customWidth="1"/>
     <col min="9" max="10" width="22" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="11.5703125" style="1"/>
+    <col min="11" max="11" width="22.109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -777,21 +789,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
@@ -800,99 +812,99 @@
         <v>2000</v>
       </c>
       <c r="K2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2"/>
+    </row>
+    <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2"/>
-    </row>
-    <row r="3" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O3"/>
     </row>
-    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>22</v>
+    <row r="4" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O4"/>
     </row>
-    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>24</v>
+    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -901,31 +913,31 @@
         <v>5000</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O5"/>
     </row>
-    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I6" s="5">
         <v>-4</v>
@@ -934,60 +946,60 @@
         <v>15</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O6"/>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7"/>
     </row>
-    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I8" s="5">
         <v>-18</v>
@@ -996,28 +1008,28 @@
         <v>15</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O8"/>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I9" s="5">
         <v>10</v>
@@ -1027,21 +1039,21 @@
       </c>
       <c r="O9"/>
     </row>
-    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>39</v>
+    <row r="10" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I10" s="5">
         <v>0.1</v>
@@ -1049,21 +1061,21 @@
       <c r="J10" s="5"/>
       <c r="O10"/>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
-        <v>43</v>
+    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3">
         <v>9.81</v>
@@ -1072,24 +1084,24 @@
       <c r="J11" s="5"/>
       <c r="O11"/>
     </row>
-    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I12" s="5">
         <v>1.5</v>
@@ -1098,37 +1110,37 @@
         <v>4000</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O12"/>
     </row>
-    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I13" s="5">
         <v>1.5</v>
@@ -1137,22 +1149,22 @@
         <v>60</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O13"/>
     </row>
-    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I14" s="5">
         <v>1</v>
@@ -1162,24 +1174,24 @@
       </c>
       <c r="O14"/>
     </row>
-    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
-        <v>56</v>
+    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I15" s="6">
         <v>1.4999999999999999E-4</v>
@@ -1188,158 +1200,158 @@
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O15"/>
     </row>
-    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O16"/>
     </row>
-    <row r="17" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O17"/>
     </row>
-    <row r="18" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="L18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O18"/>
     </row>
-    <row r="19" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="M19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O19"/>
     </row>
-    <row r="20" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="N20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O20"/>
     </row>
-    <row r="21" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H21" s="5">
         <v>0.3</v>
@@ -1347,25 +1359,25 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="M21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O21"/>
     </row>
-    <row r="22" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>73</v>
+    <row r="22" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="5">
         <v>0.3</v>
@@ -1373,57 +1385,57 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="N22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O22"/>
     </row>
-    <row r="23" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>75</v>
+    <row r="23" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O23"/>
     </row>
-    <row r="24" spans="2:15" s="3" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" s="3" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H24" s="3">
         <v>0.25</v>
@@ -1432,107 +1444,107 @@
       <c r="J24" s="5"/>
       <c r="O24"/>
     </row>
-    <row r="25" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O25"/>
     </row>
-    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="3" t="s">
-        <v>83</v>
+    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O26"/>
     </row>
-    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
-        <v>85</v>
+    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="N27" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O27"/>
     </row>
-    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="N28" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O28"/>
     </row>
-    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H29" s="5">
         <v>37</v>
@@ -1540,25 +1552,25 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="N29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O29"/>
     </row>
-    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>92</v>
+    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="7" t="s">
+        <v>127</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H30" s="6">
         <v>2.0799999999999999E-4</v>
@@ -1566,25 +1578,25 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="N30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O30"/>
     </row>
-    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H31" s="3">
         <v>9.81</v>
@@ -1592,25 +1604,25 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="N31" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O31"/>
     </row>
-    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H32" s="6">
         <v>1.33E-6</v>
@@ -1618,25 +1630,25 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="N32" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O32"/>
     </row>
-    <row r="33" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>100</v>
+    <row r="33" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H33" s="5">
         <v>26</v>
@@ -1644,353 +1656,353 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="N33" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O33"/>
     </row>
-    <row r="34" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="3" t="s">
-        <v>102</v>
+    <row r="34" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="L34" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O34"/>
     </row>
-    <row r="35" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
-        <v>104</v>
+    <row r="35" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="7" t="s">
+        <v>130</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="N35" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O35"/>
     </row>
-    <row r="36" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="3" t="s">
-        <v>106</v>
+    <row r="36" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="M36" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O36"/>
     </row>
-    <row r="37" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="3" t="s">
-        <v>108</v>
+    <row r="37" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="N37" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O37"/>
     </row>
-    <row r="38" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="L38" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O38"/>
     </row>
-    <row r="39" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="M39" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O39"/>
     </row>
-    <row r="40" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="N40" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O40"/>
     </row>
-    <row r="41" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
-        <v>116</v>
+    <row r="41" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="L41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O41"/>
     </row>
-    <row r="42" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O42"/>
     </row>
-    <row r="43" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O43"/>
     </row>
-    <row r="44" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="3" t="s">
-        <v>122</v>
+    <row r="44" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="O44"/>
-    </row>
-    <row r="45" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O45"/>
     </row>
-    <row r="46" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O46"/>
     </row>
-    <row r="47" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="O47"/>
     </row>
-    <row r="48" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B48" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="L48" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O48"/>
     </row>
-    <row r="49" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="M49" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O49"/>
     </row>
-    <row r="50" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="3" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="N50" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="O50"/>
     </row>
